--- a/obs.xlsx
+++ b/obs.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20373"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JGOR\Documents\SVAR50_APP\SVAR504B_APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92E29E0C-A561-4777-8A11-4B840ED85746}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD07AA29-8A7D-4890-B7EA-0A656CA97658}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="obs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -331,9 +331,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -823,12 +823,12 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1185,7 +1185,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD114"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1252,26 +1252,26 @@
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
